--- a/output/pdf_financials_xlsx/AW.xlsx
+++ b/output/pdf_financials_xlsx/AW.xlsx
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>54.863</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>44.036</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>54.863</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>44.036</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>299.314</v>
+        <v>244.451</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>292.299</v>
+        <v>248.263</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>294.095</v>
@@ -6723,7 +6723,11 @@
           <t>Royalty expense 27</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -7199,7 +7203,11 @@
           <t>Royalty expense 26</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
         <v>54.863</v>
       </c>

--- a/output/pdf_financials_xlsx/AW.xlsx
+++ b/output/pdf_financials_xlsx/AW.xlsx
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.763</v>
+        <v>2.516</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.95</v>
+        <v>2.605</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.435</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="29">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>70.742</v>
+        <v>72.495</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.755</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>105.594</v>
+        <v>105.973</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>23.63471137334037</v>
+        <v>24.22038394462003</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>26.37710016113637</v>
+        <v>26.60118577210322</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>35.90472466379912</v>
+        <v>36.03359458678318</v>
       </c>
     </row>
     <row r="31">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.516</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>2.605</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="101">
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-11.131</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-11.318</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="127">
@@ -4901,7 +4901,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>2.516</v>
       </c>
@@ -5682,7 +5686,11 @@
           <t>Proceeds from disposal of plant and equipment 11</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -5976,7 +5984,11 @@
           <t>Dividends paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>-11.131</v>
       </c>
@@ -6340,7 +6352,11 @@
           <t>Proceeds from disposal of plant and equipment 11</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AW.xlsx
+++ b/output/pdf_financials_xlsx/AW.xlsx
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>35.202</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>18.372</v>
       </c>
     </row>
     <row r="65">
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>27.102</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="68">
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>27.836</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>35.61</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>42.085</v>
       </c>
     </row>
     <row r="71">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>27.836</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>35.61</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>42.085</v>
       </c>
     </row>
     <row r="72">
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>56.565</v>
+        <v>28.729</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>53.337</v>
+        <v>17.727</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>60.767</v>
+        <v>18.682</v>
       </c>
     </row>
     <row r="76">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>-2.489107519325369</v>
+        <v>-2.605544958672155</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.947842390841169</v>
+        <v>3.116445555523991</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.838518845091459</v>
+        <v>3.02784700790873</v>
       </c>
     </row>
     <row r="81">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-3.011</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-1.927</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.274</v>
       </c>
     </row>
     <row r="117">
@@ -3145,7 +3145,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4316,7 +4320,11 @@
           <t>Lease liabilities 14 35,610</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>27.836</v>
       </c>
@@ -5568,7 +5576,11 @@
           <t>Purchase of intangible assets 12</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>-3.011</v>
       </c>
